--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/89.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/89.xlsx
@@ -426,13 +426,13 @@
         <v>-9.178618636207926</v>
       </c>
       <c r="E2">
-        <v>-11.65370841379272</v>
+        <v>-8.698380991646971</v>
       </c>
       <c r="F2">
-        <v>-3.611538715892668</v>
+        <v>-3.500129927155357</v>
       </c>
       <c r="G2">
-        <v>-4.956782804635194</v>
+        <v>-4.169312598919379</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.751299970508017</v>
       </c>
       <c r="E3">
-        <v>-11.89724974592523</v>
+        <v>-10.11263248119044</v>
       </c>
       <c r="F3">
-        <v>-3.342060859353155</v>
+        <v>-3.081969233854764</v>
       </c>
       <c r="G3">
-        <v>-5.045959844177784</v>
+        <v>-4.121373951935892</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.310500560885615</v>
       </c>
       <c r="E4">
-        <v>-13.12921204276394</v>
+        <v>-9.851479913642097</v>
       </c>
       <c r="F4">
-        <v>-3.444175365831056</v>
+        <v>-2.949200991636267</v>
       </c>
       <c r="G4">
-        <v>-4.754318309531218</v>
+        <v>-4.135955700546064</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.904981852498454</v>
       </c>
       <c r="E5">
-        <v>-14.31992899834078</v>
+        <v>-11.03157759767095</v>
       </c>
       <c r="F5">
-        <v>-3.210526056197427</v>
+        <v>-2.625691214514351</v>
       </c>
       <c r="G5">
-        <v>-4.646969864992425</v>
+        <v>-4.144998747163894</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.501563416081802</v>
       </c>
       <c r="E6">
-        <v>-14.16073502307514</v>
+        <v>-11.55823459628901</v>
       </c>
       <c r="F6">
-        <v>-3.188122031421312</v>
+        <v>-3.336773390221086</v>
       </c>
       <c r="G6">
-        <v>-4.143751882971305</v>
+        <v>-3.758536471892495</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.093143303140202</v>
       </c>
       <c r="E7">
-        <v>-14.93991331778292</v>
+        <v>-12.80714697133842</v>
       </c>
       <c r="F7">
-        <v>-3.13791965334205</v>
+        <v>-2.748981276910015</v>
       </c>
       <c r="G7">
-        <v>-4.435308105857325</v>
+        <v>-3.824528399896047</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.663027789695649</v>
       </c>
       <c r="E8">
-        <v>-14.71527383615842</v>
+        <v>-12.517605400236</v>
       </c>
       <c r="F8">
-        <v>-3.229104680307414</v>
+        <v>-2.760165893582614</v>
       </c>
       <c r="G8">
-        <v>-3.941727071556294</v>
+        <v>-3.812128663622905</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.213757820646326</v>
       </c>
       <c r="E9">
-        <v>-15.89231027175809</v>
+        <v>-14.92194886139449</v>
       </c>
       <c r="F9">
-        <v>-3.249926523344183</v>
+        <v>-3.204426787010615</v>
       </c>
       <c r="G9">
-        <v>-3.890274236282641</v>
+        <v>-3.084862311079782</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.755542901766733</v>
       </c>
       <c r="E10">
-        <v>-15.67691340558325</v>
+        <v>-14.04585216597455</v>
       </c>
       <c r="F10">
-        <v>-3.061929369646238</v>
+        <v>-2.668117707783533</v>
       </c>
       <c r="G10">
-        <v>-3.354755909230347</v>
+        <v>-2.102707386577433</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.300500860231647</v>
       </c>
       <c r="E11">
-        <v>-17.36192235604533</v>
+        <v>-15.5795874422104</v>
       </c>
       <c r="F11">
-        <v>-3.111258648482949</v>
+        <v>-2.464229982197685</v>
       </c>
       <c r="G11">
-        <v>-3.05751332938181</v>
+        <v>-2.691834311467934</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.866653533441172</v>
       </c>
       <c r="E12">
-        <v>-17.16338047012704</v>
+        <v>-14.94620336817957</v>
       </c>
       <c r="F12">
-        <v>-2.876604529189724</v>
+        <v>-1.996853496394565</v>
       </c>
       <c r="G12">
-        <v>-1.953290400424999</v>
+        <v>-1.896000271997094</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.461641841403634</v>
       </c>
       <c r="E13">
-        <v>-18.15330035972977</v>
+        <v>-16.60719782097897</v>
       </c>
       <c r="F13">
-        <v>-2.979930108810517</v>
+        <v>-2.419877534716994</v>
       </c>
       <c r="G13">
-        <v>-1.720389294135613</v>
+        <v>-1.110731765947666</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.099582002698194</v>
       </c>
       <c r="E14">
-        <v>-19.16338554408866</v>
+        <v>-16.9669352676743</v>
       </c>
       <c r="F14">
-        <v>-2.931568363100277</v>
+        <v>-2.333858206875488</v>
       </c>
       <c r="G14">
-        <v>-1.715802146395509</v>
+        <v>-0.6277228275111657</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.786684073508466</v>
       </c>
       <c r="E15">
-        <v>-19.97238836861095</v>
+        <v>-17.42056156597065</v>
       </c>
       <c r="F15">
-        <v>-2.657574247480701</v>
+        <v>-2.438668220882098</v>
       </c>
       <c r="G15">
-        <v>-0.4713398079880305</v>
+        <v>-0.5992647929261017</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.526124381481771</v>
       </c>
       <c r="E16">
-        <v>-20.30700636998573</v>
+        <v>-18.41478803435468</v>
       </c>
       <c r="F16">
-        <v>-2.484014709246149</v>
+        <v>-2.176405444420969</v>
       </c>
       <c r="G16">
-        <v>-0.5037221835581904</v>
+        <v>1.133971590197821</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.320191368598116</v>
       </c>
       <c r="E17">
-        <v>-21.0697689464157</v>
+        <v>-18.59306499908865</v>
       </c>
       <c r="F17">
-        <v>-2.225199597915471</v>
+        <v>-1.611845723288814</v>
       </c>
       <c r="G17">
-        <v>0.1074250192177445</v>
+        <v>1.802284234982402</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.163199305017848</v>
       </c>
       <c r="E18">
-        <v>-21.76656524197594</v>
+        <v>-20.30979590997446</v>
       </c>
       <c r="F18">
-        <v>-2.284737676624283</v>
+        <v>-1.490885030029822</v>
       </c>
       <c r="G18">
-        <v>0.03194379846427831</v>
+        <v>0.9154750465543975</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.051866576555625</v>
       </c>
       <c r="E19">
-        <v>-22.70715646421312</v>
+        <v>-20.82663517694388</v>
       </c>
       <c r="F19">
-        <v>-1.975169322891483</v>
+        <v>-1.449554466834543</v>
       </c>
       <c r="G19">
-        <v>0.6524654512355468</v>
+        <v>1.508591936861184</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.973703566445136</v>
       </c>
       <c r="E20">
-        <v>-22.65244796972646</v>
+        <v>-21.52534701700937</v>
       </c>
       <c r="F20">
-        <v>-1.580481248316616</v>
+        <v>-0.9493033922839216</v>
       </c>
       <c r="G20">
-        <v>0.9622882345429952</v>
+        <v>1.972185887330449</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.918928150213451</v>
       </c>
       <c r="E21">
-        <v>-24.68480446199887</v>
+        <v>-21.91057977236787</v>
       </c>
       <c r="F21">
-        <v>-1.2342170470072</v>
+        <v>-0.9613851308537524</v>
       </c>
       <c r="G21">
-        <v>0.6311539172069534</v>
+        <v>1.492927385136395</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.874532847190757</v>
       </c>
       <c r="E22">
-        <v>-24.73076847317673</v>
+        <v>-23.39048960654856</v>
       </c>
       <c r="F22">
-        <v>-0.9387077448347131</v>
+        <v>-0.4818109350444094</v>
       </c>
       <c r="G22">
-        <v>0.615302335853276</v>
+        <v>1.569035319207715</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.827632804660478</v>
       </c>
       <c r="E23">
-        <v>-25.35050372654844</v>
+        <v>-23.8738679790753</v>
       </c>
       <c r="F23">
-        <v>-0.8588117088347008</v>
+        <v>-0.1841553329312687</v>
       </c>
       <c r="G23">
-        <v>0.6233708596679506</v>
+        <v>2.237108434818456</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.769346625458711</v>
       </c>
       <c r="E24">
-        <v>-24.64736756737746</v>
+        <v>-24.23243255100264</v>
       </c>
       <c r="F24">
-        <v>-0.8587313571966293</v>
+        <v>-0.01203881071239297</v>
       </c>
       <c r="G24">
-        <v>0.527582158683081</v>
+        <v>1.093179443770804</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.689224742007935</v>
       </c>
       <c r="E25">
-        <v>-25.85447759886207</v>
+        <v>-23.89557295499407</v>
       </c>
       <c r="F25">
-        <v>-0.4706959012336456</v>
+        <v>0.03939866316444234</v>
       </c>
       <c r="G25">
-        <v>0.2522942322887882</v>
+        <v>0.9108714927064965</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.583481908217051</v>
       </c>
       <c r="E26">
-        <v>-25.95399987212864</v>
+        <v>-24.49874305044572</v>
       </c>
       <c r="F26">
-        <v>-0.6232654378486614</v>
+        <v>0.05280247610914113</v>
       </c>
       <c r="G26">
-        <v>-0.606749259303195</v>
+        <v>1.898706211728244</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.446946106450614</v>
       </c>
       <c r="E27">
-        <v>-25.1704108437374</v>
+        <v>-24.55006424637465</v>
       </c>
       <c r="F27">
-        <v>-0.660439253416692</v>
+        <v>-0.02620803513727851</v>
       </c>
       <c r="G27">
-        <v>-0.3731394091569691</v>
+        <v>0.5578350214611613</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.280192155903995</v>
       </c>
       <c r="E28">
-        <v>-25.41540128755236</v>
+        <v>-25.79712900402894</v>
       </c>
       <c r="F28">
-        <v>-0.5795061014283747</v>
+        <v>0.1486710923699335</v>
       </c>
       <c r="G28">
-        <v>-1.098820931686881</v>
+        <v>0.3204944224018466</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.085061822430607</v>
       </c>
       <c r="E29">
-        <v>-26.00477312270264</v>
+        <v>-23.66927152340876</v>
       </c>
       <c r="F29">
-        <v>-0.6503588504920248</v>
+        <v>0.04394888530802002</v>
       </c>
       <c r="G29">
-        <v>-1.315680145772142</v>
+        <v>-0.3393493895378074</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.866165903556995</v>
       </c>
       <c r="E30">
-        <v>-25.89142994676466</v>
+        <v>-23.69363924204403</v>
       </c>
       <c r="F30">
-        <v>-0.5306382232350234</v>
+        <v>0.2332300084803043</v>
       </c>
       <c r="G30">
-        <v>-1.541254284319288</v>
+        <v>-0.6802092475760434</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.631077009986697</v>
       </c>
       <c r="E31">
-        <v>-25.55816143064417</v>
+        <v>-23.67589668088198</v>
       </c>
       <c r="F31">
-        <v>-0.4989647672215816</v>
+        <v>-0.3122573815697954</v>
       </c>
       <c r="G31">
-        <v>-1.504678507596158</v>
+        <v>0.1188666387955283</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.385044406530637</v>
       </c>
       <c r="E32">
-        <v>-25.25795530325368</v>
+        <v>-23.84426987296117</v>
       </c>
       <c r="F32">
-        <v>-0.4722424631746723</v>
+        <v>0.07832281905458831</v>
       </c>
       <c r="G32">
-        <v>-1.667761781543679</v>
+        <v>-0.8155333871306624</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.136158235657875</v>
       </c>
       <c r="E33">
-        <v>-24.80796084111148</v>
+        <v>-23.31715096999433</v>
       </c>
       <c r="F33">
-        <v>-0.8601271562703464</v>
+        <v>0.5272971230045176</v>
       </c>
       <c r="G33">
-        <v>-1.794846773762532</v>
+        <v>-1.500869009365642</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8899550283774929</v>
       </c>
       <c r="E34">
-        <v>-25.14328075595744</v>
+        <v>-22.08897900590005</v>
       </c>
       <c r="F34">
-        <v>-0.5568411409203774</v>
+        <v>0.2247806609717493</v>
       </c>
       <c r="G34">
-        <v>-2.343736078669563</v>
+        <v>-1.568701702664043</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.6557902943698879</v>
       </c>
       <c r="E35">
-        <v>-23.76172484874936</v>
+        <v>-22.1247856498787</v>
       </c>
       <c r="F35">
-        <v>-0.6596489909144213</v>
+        <v>-0.2046640530897788</v>
       </c>
       <c r="G35">
-        <v>-2.551184749322336</v>
+        <v>-2.457436968147441</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.4439851615923824</v>
       </c>
       <c r="E36">
-        <v>-23.4026168599411</v>
+        <v>-22.51872213227995</v>
       </c>
       <c r="F36">
-        <v>-0.4896530892467123</v>
+        <v>0.4103316457292274</v>
       </c>
       <c r="G36">
-        <v>-2.362094513294656</v>
+        <v>-1.443250758781793</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.2656289654356772</v>
       </c>
       <c r="E37">
-        <v>-22.71724590430221</v>
+        <v>-22.1702470004417</v>
       </c>
       <c r="F37">
-        <v>-0.7313624137095801</v>
+        <v>0.3518050036192339</v>
       </c>
       <c r="G37">
-        <v>-2.429247993730252</v>
+        <v>-2.128241852753031</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.1337575612712842</v>
       </c>
       <c r="E38">
-        <v>-22.94384621517203</v>
+        <v>-20.67200137500396</v>
       </c>
       <c r="F38">
-        <v>-0.4786018397259641</v>
+        <v>0.2493326424233238</v>
       </c>
       <c r="G38">
-        <v>-2.443117717262025</v>
+        <v>-2.048068485169559</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.05988307023603605</v>
       </c>
       <c r="E39">
-        <v>-21.67879435875928</v>
+        <v>-20.74812955154691</v>
       </c>
       <c r="F39">
-        <v>-0.7378253361862218</v>
+        <v>0.8054040827789928</v>
       </c>
       <c r="G39">
-        <v>-2.124835944774328</v>
+        <v>-1.798075495777026</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.05418390672354951</v>
       </c>
       <c r="E40">
-        <v>-22.07334671362557</v>
+        <v>-19.877951571655</v>
       </c>
       <c r="F40">
-        <v>-0.5946030973443956</v>
+        <v>0.2471730886042255</v>
       </c>
       <c r="G40">
-        <v>-1.887078630576964</v>
+        <v>-1.810324295858433</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1249556358762177</v>
       </c>
       <c r="E41">
-        <v>-20.3192694775985</v>
+        <v>-18.46079733027261</v>
       </c>
       <c r="F41">
-        <v>-0.4813238550115633</v>
+        <v>0.1820882617662684</v>
       </c>
       <c r="G41">
-        <v>-1.744270024645251</v>
+        <v>-2.309037160678435</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.2739497923027477</v>
       </c>
       <c r="E42">
-        <v>-21.28641114294265</v>
+        <v>-19.06514030049225</v>
       </c>
       <c r="F42">
-        <v>-0.5949344443055155</v>
+        <v>0.5328736923601638</v>
       </c>
       <c r="G42">
-        <v>-2.002167476774487</v>
+        <v>-2.241266810589664</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.5005365538594386</v>
       </c>
       <c r="E43">
-        <v>-20.13594779281999</v>
+        <v>-19.10240058462736</v>
       </c>
       <c r="F43">
-        <v>-0.5054343166374456</v>
+        <v>0.2404102971277704</v>
       </c>
       <c r="G43">
-        <v>-1.294709858785731</v>
+        <v>-2.152972419646566</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7963041798497588</v>
       </c>
       <c r="E44">
-        <v>-19.9241782343253</v>
+        <v>-17.7559267655567</v>
       </c>
       <c r="F44">
-        <v>-0.4765060701968813</v>
+        <v>0.009943575055697514</v>
       </c>
       <c r="G44">
-        <v>-1.334990134649474</v>
+        <v>-1.15561559565931</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.148888506453382</v>
       </c>
       <c r="E45">
-        <v>-19.42742727805389</v>
+        <v>-16.88362493135519</v>
       </c>
       <c r="F45">
-        <v>-0.6085428639987057</v>
+        <v>0.5966008250249326</v>
       </c>
       <c r="G45">
-        <v>-1.83001818765822</v>
+        <v>-0.7232194997772446</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.542990911659014</v>
       </c>
       <c r="E46">
-        <v>-18.5190018066932</v>
+        <v>-15.96962038001704</v>
       </c>
       <c r="F46">
-        <v>-0.3649995341060399</v>
+        <v>0.329811849074907</v>
       </c>
       <c r="G46">
-        <v>-1.083100599195582</v>
+        <v>-0.7288074200929791</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.958232963075649</v>
       </c>
       <c r="E47">
-        <v>-18.75047928406928</v>
+        <v>-14.88439875492289</v>
       </c>
       <c r="F47">
-        <v>-0.4625414525204873</v>
+        <v>0.6785677795319437</v>
       </c>
       <c r="G47">
-        <v>-1.289548497272724</v>
+        <v>-1.360970846957157</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.380064528141877</v>
       </c>
       <c r="E48">
-        <v>-17.0808807306553</v>
+        <v>-15.15319085812217</v>
       </c>
       <c r="F48">
-        <v>-0.4875954246181584</v>
+        <v>0.1096640997395076</v>
       </c>
       <c r="G48">
-        <v>-1.898854934753811</v>
+        <v>-1.40929011564154</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.789196499984425</v>
       </c>
       <c r="E49">
-        <v>-17.8304337484049</v>
+        <v>-16.19665542439159</v>
       </c>
       <c r="F49">
-        <v>-0.4719848409124017</v>
+        <v>0.2271986654205211</v>
       </c>
       <c r="G49">
-        <v>-1.541700530451372</v>
+        <v>-0.1480869848377749</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.172644972662877</v>
       </c>
       <c r="E50">
-        <v>-16.97817041168733</v>
+        <v>-14.54640251193839</v>
       </c>
       <c r="F50">
-        <v>-0.4553595071382156</v>
+        <v>0.1705814101739804</v>
       </c>
       <c r="G50">
-        <v>-1.642263408805234</v>
+        <v>-1.083143255075854</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.518911485133864</v>
       </c>
       <c r="E51">
-        <v>-16.80960249522581</v>
+        <v>-13.43391494484405</v>
       </c>
       <c r="F51">
-        <v>-0.3964277933682532</v>
+        <v>0.4188381505885755</v>
       </c>
       <c r="G51">
-        <v>-2.108715303252776</v>
+        <v>-0.8761342681120468</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.821559857843297</v>
       </c>
       <c r="E52">
-        <v>-16.68405508183715</v>
+        <v>-14.37713268200567</v>
       </c>
       <c r="F52">
-        <v>-0.3736915932636151</v>
+        <v>0.3525637881601982</v>
       </c>
       <c r="G52">
-        <v>-1.481910111195171</v>
+        <v>-0.2112078439768129</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.0813637212345</v>
       </c>
       <c r="E53">
-        <v>-14.55268803386103</v>
+        <v>-14.09773036420642</v>
       </c>
       <c r="F53">
-        <v>-0.6201242686572457</v>
+        <v>-0.02245718753740235</v>
       </c>
       <c r="G53">
-        <v>-2.067601597112934</v>
+        <v>-1.375030881339378</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.298092271569022</v>
       </c>
       <c r="E54">
-        <v>-14.77484138325532</v>
+        <v>-13.5565097931797</v>
       </c>
       <c r="F54">
-        <v>-0.5787531154592299</v>
+        <v>0.4629520282572603</v>
       </c>
       <c r="G54">
-        <v>-1.921482238627741</v>
+        <v>-2.099281791269372</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.479658059942088</v>
       </c>
       <c r="E55">
-        <v>-15.99509304631019</v>
+        <v>-13.32935248000694</v>
       </c>
       <c r="F55">
-        <v>-0.6282546947157228</v>
+        <v>0.5510373044013486</v>
       </c>
       <c r="G55">
-        <v>-2.23177751783975</v>
+        <v>-1.378381008551571</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.629376985618808</v>
       </c>
       <c r="E56">
-        <v>-14.31651000046499</v>
+        <v>-11.81424281736464</v>
       </c>
       <c r="F56">
-        <v>-0.5130677222542431</v>
+        <v>0.6766426536878376</v>
       </c>
       <c r="G56">
-        <v>-2.588091929422971</v>
+        <v>-1.736690402842934</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.755590615973957</v>
       </c>
       <c r="E57">
-        <v>-14.16545822146514</v>
+        <v>-11.67232949891226</v>
       </c>
       <c r="F57">
-        <v>-0.2502234318763488</v>
+        <v>0.154560784603838</v>
       </c>
       <c r="G57">
-        <v>-2.814479810916859</v>
+        <v>-2.168003695610382</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.863367621955645</v>
       </c>
       <c r="E58">
-        <v>-13.66547393475226</v>
+        <v>-11.2383024361211</v>
       </c>
       <c r="F58">
-        <v>-0.2491540095593346</v>
+        <v>0.6627037154009303</v>
       </c>
       <c r="G58">
-        <v>-2.433680924057062</v>
+        <v>-2.704578576004817</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.95737210265658</v>
       </c>
       <c r="E59">
-        <v>-13.14077323690552</v>
+        <v>-10.98873370508438</v>
       </c>
       <c r="F59">
-        <v>-0.366883241580006</v>
+        <v>0.573168796301943</v>
       </c>
       <c r="G59">
-        <v>-2.528879005161231</v>
+        <v>-3.111833952298417</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.041257933387959</v>
       </c>
       <c r="E60">
-        <v>-13.49415723456809</v>
+        <v>-9.807734854728</v>
       </c>
       <c r="F60">
-        <v>-0.5041039585885497</v>
+        <v>0.5234344458052634</v>
       </c>
       <c r="G60">
-        <v>-3.23194634870345</v>
+        <v>-3.026450004878547</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.115189659596315</v>
       </c>
       <c r="E61">
-        <v>-12.54544645843515</v>
+        <v>-10.30079057620914</v>
       </c>
       <c r="F61">
-        <v>-0.2674360781391197</v>
+        <v>0.4675867438759236</v>
       </c>
       <c r="G61">
-        <v>-2.923859331600948</v>
+        <v>-2.591576586719101</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.180270552708645</v>
       </c>
       <c r="E62">
-        <v>-11.96078423625285</v>
+        <v>-9.528762741959476</v>
       </c>
       <c r="F62">
-        <v>-0.340126974469582</v>
+        <v>0.8704325806335595</v>
       </c>
       <c r="G62">
-        <v>-4.611706576893073</v>
+        <v>-2.656548054817665</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.2312738518457</v>
       </c>
       <c r="E63">
-        <v>-12.55905905130221</v>
+        <v>-9.583684074724502</v>
       </c>
       <c r="F63">
-        <v>-0.595746244360259</v>
+        <v>0.5623486612865758</v>
       </c>
       <c r="G63">
-        <v>-3.721074765348315</v>
+        <v>-4.013165827348524</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.266423427082078</v>
       </c>
       <c r="E64">
-        <v>-11.85038003994585</v>
+        <v>-9.27691166002289</v>
       </c>
       <c r="F64">
-        <v>-0.5355421582595965</v>
+        <v>-0.1787543774650159</v>
       </c>
       <c r="G64">
-        <v>-3.80294452447802</v>
+        <v>-4.369020867913422</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.280655363512711</v>
       </c>
       <c r="E65">
-        <v>-11.97912908445792</v>
+        <v>-9.746677439682582</v>
       </c>
       <c r="F65">
-        <v>-0.5233336794771374</v>
+        <v>0.3666220113531086</v>
       </c>
       <c r="G65">
-        <v>-4.157562544515008</v>
+        <v>-4.696214438156571</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.272798680044336</v>
       </c>
       <c r="E66">
-        <v>-11.48986822419521</v>
+        <v>-10.36562021010295</v>
       </c>
       <c r="F66">
-        <v>-0.8222293475922691</v>
+        <v>0.1561562202216298</v>
       </c>
       <c r="G66">
-        <v>-3.687586618112622</v>
+        <v>-3.449976958885433</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.241152857305571</v>
       </c>
       <c r="E67">
-        <v>-11.90217219717157</v>
+        <v>-8.991327975203166</v>
       </c>
       <c r="F67">
-        <v>-0.7284565008605594</v>
+        <v>0.3336935787244255</v>
       </c>
       <c r="G67">
-        <v>-4.081644921294135</v>
+        <v>-4.325039374130625</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.186569780582099</v>
       </c>
       <c r="E68">
-        <v>-10.64988158051243</v>
+        <v>-8.889763360159135</v>
       </c>
       <c r="F68">
-        <v>-0.7563815943763336</v>
+        <v>0.01196396315112551</v>
       </c>
       <c r="G68">
-        <v>-4.340228148729294</v>
+        <v>-3.537237765037306</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.113485213632047</v>
       </c>
       <c r="E69">
-        <v>-10.20576960610619</v>
+        <v>-8.919334295429222</v>
       </c>
       <c r="F69">
-        <v>-0.8215268920346951</v>
+        <v>-0.004479129794444679</v>
       </c>
       <c r="G69">
-        <v>-5.157255598252589</v>
+        <v>-3.851263793162403</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.026048044707897</v>
       </c>
       <c r="E70">
-        <v>-10.88684756838581</v>
+        <v>-9.277871696512515</v>
       </c>
       <c r="F70">
-        <v>-0.9422937473214321</v>
+        <v>-0.05857400629946079</v>
       </c>
       <c r="G70">
-        <v>-4.451904524504996</v>
+        <v>-3.061322827612325</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.934888304192422</v>
       </c>
       <c r="E71">
-        <v>-11.26247090190004</v>
+        <v>-7.569645259813111</v>
       </c>
       <c r="F71">
-        <v>-1.14103565460109</v>
+        <v>-0.4949877753207411</v>
       </c>
       <c r="G71">
-        <v>-3.910306093903051</v>
+        <v>-4.271079685585557</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.847355282385079</v>
       </c>
       <c r="E72">
-        <v>-11.79979698528017</v>
+        <v>-9.674221855559855</v>
       </c>
       <c r="F72">
-        <v>-1.339712949223329</v>
+        <v>0.04221345559915506</v>
       </c>
       <c r="G72">
-        <v>-4.180675469179736</v>
+        <v>-3.587125457627103</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.773149351530826</v>
       </c>
       <c r="E73">
-        <v>-11.24423020859714</v>
+        <v>-8.423375822109165</v>
       </c>
       <c r="F73">
-        <v>-1.533101946346096</v>
+        <v>-0.05006584470530707</v>
       </c>
       <c r="G73">
-        <v>-3.725894879819139</v>
+        <v>-4.848981551521198</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.717591548309822</v>
       </c>
       <c r="E74">
-        <v>-11.46427328910386</v>
+        <v>-9.80965945618126</v>
       </c>
       <c r="F74">
-        <v>-1.27893894634954</v>
+        <v>-0.4694980819691976</v>
       </c>
       <c r="G74">
-        <v>-4.316025858506831</v>
+        <v>-3.805763093797583</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.684101194839212</v>
       </c>
       <c r="E75">
-        <v>-11.80922526816414</v>
+        <v>-10.40205178349466</v>
       </c>
       <c r="F75">
-        <v>-1.297865484768703</v>
+        <v>0.01614473343305461</v>
       </c>
       <c r="G75">
-        <v>-3.943436587988764</v>
+        <v>-3.274661290964302</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.674228323574459</v>
       </c>
       <c r="E76">
-        <v>-12.453255784587</v>
+        <v>-10.10634243079378</v>
       </c>
       <c r="F76">
-        <v>-1.431917696461539</v>
+        <v>-0.3869570688520464</v>
       </c>
       <c r="G76">
-        <v>-3.989163691641186</v>
+        <v>-3.385491111577666</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.682829766672853</v>
       </c>
       <c r="E77">
-        <v>-12.17826872894523</v>
+        <v>-9.901596535484984</v>
       </c>
       <c r="F77">
-        <v>-1.520212549558535</v>
+        <v>-0.4281559216302798</v>
       </c>
       <c r="G77">
-        <v>-3.940798485854971</v>
+        <v>-2.921972629204268</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.704625429571826</v>
       </c>
       <c r="E78">
-        <v>-12.56286749794266</v>
+        <v>-10.1918400200586</v>
       </c>
       <c r="F78">
-        <v>-1.37231831856492</v>
+        <v>-0.5718080831541589</v>
       </c>
       <c r="G78">
-        <v>-3.665608996107461</v>
+        <v>-2.26498676124289</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.726988157803693</v>
       </c>
       <c r="E79">
-        <v>-12.69494949932438</v>
+        <v>-11.1444271699421</v>
       </c>
       <c r="F79">
-        <v>-1.25778824145386</v>
+        <v>-0.09938932497019803</v>
       </c>
       <c r="G79">
-        <v>-3.555002298560139</v>
+        <v>-2.996302141190369</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.739404025598181</v>
       </c>
       <c r="E80">
-        <v>-13.3847674164388</v>
+        <v>-11.30420078988072</v>
       </c>
       <c r="F80">
-        <v>-1.439947890064277</v>
+        <v>-0.7082136866383478</v>
       </c>
       <c r="G80">
-        <v>-2.451117335423951</v>
+        <v>-2.054352024455896</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.728657113838061</v>
       </c>
       <c r="E81">
-        <v>-13.56791701920502</v>
+        <v>-12.86568202636157</v>
       </c>
       <c r="F81">
-        <v>-1.509593707822048</v>
+        <v>-0.72735891405185</v>
       </c>
       <c r="G81">
-        <v>-3.08167952616712</v>
+        <v>-2.76601616848386</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.684649257371671</v>
       </c>
       <c r="E82">
-        <v>-14.95199075796137</v>
+        <v>-13.14724442626248</v>
       </c>
       <c r="F82">
-        <v>-1.781155736747005</v>
+        <v>-0.6257389429134207</v>
       </c>
       <c r="G82">
-        <v>-2.832953088296533</v>
+        <v>-2.471421534433795</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.600415130347694</v>
       </c>
       <c r="E83">
-        <v>-16.13695202307447</v>
+        <v>-12.64415813485435</v>
       </c>
       <c r="F83">
-        <v>-1.848113502282692</v>
+        <v>-0.6189645542933263</v>
       </c>
       <c r="G83">
-        <v>-2.856361322901611</v>
+        <v>-1.720386012914053</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.469900496361739</v>
       </c>
       <c r="E84">
-        <v>-16.64414564040755</v>
+        <v>-14.78176994848705</v>
       </c>
       <c r="F84">
-        <v>-2.135243039808459</v>
+        <v>-0.7265935025716633</v>
       </c>
       <c r="G84">
-        <v>-3.013407149179754</v>
+        <v>-1.249737436091982</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.293783941143145</v>
       </c>
       <c r="E85">
-        <v>-18.65267330245161</v>
+        <v>-15.79598510114094</v>
       </c>
       <c r="F85">
-        <v>-1.891769292777628</v>
+        <v>-1.039864658594978</v>
       </c>
       <c r="G85">
-        <v>-2.82020226131653</v>
+        <v>-2.513683668119443</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.073174878431192</v>
       </c>
       <c r="E86">
-        <v>-18.55710438699374</v>
+        <v>-17.68443574639761</v>
       </c>
       <c r="F86">
-        <v>-1.767907656874032</v>
+        <v>-1.246304584148851</v>
       </c>
       <c r="G86">
-        <v>-2.30764920395879</v>
+        <v>-1.355861984989102</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.816927307669324</v>
       </c>
       <c r="E87">
-        <v>-20.16466737497664</v>
+        <v>-18.57645908490252</v>
       </c>
       <c r="F87">
-        <v>-2.027993483800604</v>
+        <v>-0.8278945522600148</v>
       </c>
       <c r="G87">
-        <v>-2.576814370923159</v>
+        <v>-1.74232754148206</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.538247207077627</v>
       </c>
       <c r="E88">
-        <v>-21.49608854644581</v>
+        <v>-20.54726908693669</v>
       </c>
       <c r="F88">
-        <v>-2.005234089408688</v>
+        <v>-0.6423717319942319</v>
       </c>
       <c r="G88">
-        <v>-2.072352805931009</v>
+        <v>-1.658672797824017</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.255382043284714</v>
       </c>
       <c r="E89">
-        <v>-22.6723687268862</v>
+        <v>-20.39062917101137</v>
       </c>
       <c r="F89">
-        <v>-1.956140895281775</v>
+        <v>-0.8186292628597024</v>
       </c>
       <c r="G89">
-        <v>-1.950061678410505</v>
+        <v>-1.200778329203507</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.992543695160061</v>
       </c>
       <c r="E90">
-        <v>-23.63494116195661</v>
+        <v>-21.57890980757209</v>
       </c>
       <c r="F90">
-        <v>-2.048111214544993</v>
+        <v>-1.133189358561773</v>
       </c>
       <c r="G90">
-        <v>-2.265455975925891</v>
+        <v>-1.064778258007642</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.772756115977737</v>
       </c>
       <c r="E91">
-        <v>-25.40745834414291</v>
+        <v>-24.22280501526233</v>
       </c>
       <c r="F91">
-        <v>-2.194548347277084</v>
+        <v>-1.914588329622546</v>
       </c>
       <c r="G91">
-        <v>-2.304732197992444</v>
+        <v>-1.909230157324775</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.621630629000015</v>
       </c>
       <c r="E92">
-        <v>-27.5525059120962</v>
+        <v>-25.545069612288</v>
       </c>
       <c r="F92">
-        <v>-2.31235296073141</v>
+        <v>-1.756608725499847</v>
       </c>
       <c r="G92">
-        <v>-1.776163498203054</v>
+        <v>-1.774112734728401</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.560184160663401</v>
       </c>
       <c r="E93">
-        <v>-29.61268308443475</v>
+        <v>-27.31411798338442</v>
       </c>
       <c r="F93">
-        <v>-2.395695833494471</v>
+        <v>-1.420640302639826</v>
       </c>
       <c r="G93">
-        <v>-2.455487922541131</v>
+        <v>-1.229144489584906</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.60492302215292</v>
       </c>
       <c r="E94">
-        <v>-31.64440559034609</v>
+        <v>-29.82061249697094</v>
       </c>
       <c r="F94">
-        <v>-2.604545479823088</v>
+        <v>-1.960923060298137</v>
       </c>
       <c r="G94">
-        <v>-2.315304293856975</v>
+        <v>-1.898658061460244</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.767487670822817</v>
       </c>
       <c r="E95">
-        <v>-33.2598843508944</v>
+        <v>-32.83940874657119</v>
       </c>
       <c r="F95">
-        <v>-2.565023242668121</v>
+        <v>-1.746426433384636</v>
       </c>
       <c r="G95">
-        <v>-3.134618754807201</v>
+        <v>-2.46382550652368</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.054803491101294</v>
       </c>
       <c r="E96">
-        <v>-35.92840992871236</v>
+        <v>-34.73451172014513</v>
       </c>
       <c r="F96">
-        <v>-2.770276117733782</v>
+        <v>-2.195113293845793</v>
       </c>
       <c r="G96">
-        <v>-2.988299241806883</v>
+        <v>-1.874675613082263</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.454593962026472</v>
       </c>
       <c r="E97">
-        <v>-37.8819596520663</v>
+        <v>-36.51464579561233</v>
       </c>
       <c r="F97">
-        <v>-3.111896491383104</v>
+        <v>-2.427501828292361</v>
       </c>
       <c r="G97">
-        <v>-3.55251513261808</v>
+        <v>-2.358508138130183</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.969405796524105</v>
       </c>
       <c r="E98">
-        <v>-40.59807269899387</v>
+        <v>-39.61942644543323</v>
       </c>
       <c r="F98">
-        <v>-2.684025675386895</v>
+        <v>-2.218034219881256</v>
       </c>
       <c r="G98">
-        <v>-3.406983112792029</v>
+        <v>-3.541135856249926</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.554878032105914</v>
       </c>
       <c r="E99">
-        <v>-43.19438496604852</v>
+        <v>-41.81217922282033</v>
       </c>
       <c r="F99">
-        <v>-2.798863905171796</v>
+        <v>-2.508309068435453</v>
       </c>
       <c r="G99">
-        <v>-3.332233604446319</v>
+        <v>-2.906157141287744</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.23269760142824</v>
       </c>
       <c r="E100">
-        <v>-44.78036071843685</v>
+        <v>-44.23246744095983</v>
       </c>
       <c r="F100">
-        <v>-3.371062002125166</v>
+        <v>-2.849921158410746</v>
       </c>
       <c r="G100">
-        <v>-4.894396939125472</v>
+        <v>-3.133083143117381</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.90928575129882</v>
       </c>
       <c r="E101">
-        <v>-47.15709180933357</v>
+        <v>-46.29729082763023</v>
       </c>
       <c r="F101">
-        <v>-3.176627605340066</v>
+        <v>-3.010293087592731</v>
       </c>
       <c r="G101">
-        <v>-5.112092864708392</v>
+        <v>-4.208903818255639</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.68286069420748</v>
       </c>
       <c r="E102">
-        <v>-49.84898318091262</v>
+        <v>-48.07997443396376</v>
       </c>
       <c r="F102">
-        <v>-3.578915950835618</v>
+        <v>-2.621053185426077</v>
       </c>
       <c r="G102">
-        <v>-4.98977876863697</v>
+        <v>-4.554291762045908</v>
       </c>
     </row>
   </sheetData>
